--- a/estimates/安楽寺本堂_空調換気設備工事/御見積書_安楽寺本堂新築工事_空調換気設備工事_20261009.xlsx
+++ b/estimates/安楽寺本堂_空調換気設備工事/御見積書_安楽寺本堂新築工事_空調換気設備工事_20261009.xlsx
@@ -188,12 +188,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -782,7 +782,7 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -791,7 +791,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -808,7 +808,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -818,7 +818,7 @@
     <xf numFmtId="171" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1008,7 +1008,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1072,10 +1072,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1105,10 +1105,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1130,23 +1130,23 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1299,7 +1299,7 @@
     <xf numFmtId="174" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1314,7 +1314,7 @@
     <xf numFmtId="174" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B7" s="15" t="str">
         <f>"¥"&amp;TEXT(K30,"#,##0")&amp;"-"</f>
-        <v>¥3,930,000-</v>
+        <v>¥2,810,000-</v>
       </c>
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="N13" s="26">
         <f>IF(TARGET="",ROUNDUP(COST_TOTAL/(1-TARGET_MARGIN)/ROUND_UNIT,0)*ROUND_UNIT,TARGET)</f>
-        <v>3930000</v>
+        <v>2810000</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I22" s="45">
         <f>K22</f>
-        <v>2245200</v>
+        <v>1086750</v>
       </c>
       <c r="J22" s="38" t="n"/>
       <c r="K22" s="45">
         <f>'内訳書(空調設備工事)'!H11</f>
-        <v>2245200</v>
+        <v>1086750</v>
       </c>
       <c r="L22" s="46" t="inlineStr">
         <is>
@@ -2188,19 +2188,19 @@
       </c>
       <c r="N22" s="48">
         <f>K22</f>
-        <v>2245200</v>
+        <v>1086750</v>
       </c>
       <c r="O22" s="48">
         <f>'内訳書(空調設備工事)'!P11</f>
-        <v>1683900</v>
+        <v>869400</v>
       </c>
       <c r="P22" s="48">
         <f>N22-O22</f>
-        <v>561300</v>
+        <v>217350</v>
       </c>
       <c r="Q22" s="49">
         <f>IF(N22=0,"",P22/N22)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="I25" s="45">
         <f>K25</f>
-        <v>385560</v>
+        <v>257040</v>
       </c>
       <c r="J25" s="38" t="n"/>
       <c r="K25" s="45">
         <f>'内訳書(空調設備工事)'!H77</f>
-        <v>385560</v>
+        <v>257040</v>
       </c>
       <c r="L25" s="46" t="inlineStr">
         <is>
@@ -2365,19 +2365,19 @@
       </c>
       <c r="N25" s="48">
         <f>K25</f>
-        <v>385560</v>
+        <v>257040</v>
       </c>
       <c r="O25" s="48">
         <f>'内訳書(空調設備工事)'!P77</f>
-        <v>289170</v>
+        <v>205632</v>
       </c>
       <c r="P25" s="48">
         <f>N25-O25</f>
-        <v>96390</v>
+        <v>51408</v>
       </c>
       <c r="Q25" s="49">
         <f>IF(N25=0,"",P25/N25)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
@@ -2514,7 +2514,7 @@
       <c r="J28" s="59" t="n"/>
       <c r="K28" s="60">
         <f>SUM(K22:K27)</f>
-        <v>4173260</v>
+        <v>2886290</v>
       </c>
       <c r="L28" s="61" t="n"/>
       <c r="M28" s="47" t="inlineStr">
@@ -2551,7 +2551,7 @@
       <c r="J29" s="64" t="n"/>
       <c r="K29" s="65">
         <f>IF(SUBMIT&lt;K28,SUBMIT-K28,0)</f>
-        <v>-243260</v>
+        <v>-76290</v>
       </c>
       <c r="L29" s="66" t="n"/>
       <c r="M29" s="67" t="inlineStr">
@@ -2561,11 +2561,11 @@
       </c>
       <c r="N29" s="48">
         <f>K28</f>
-        <v>4173260</v>
+        <v>2886290</v>
       </c>
       <c r="O29" s="68">
         <f>SUM(O22:O28)</f>
-        <v>3140677</v>
+        <v>2242639</v>
       </c>
       <c r="P29" s="40" t="n"/>
       <c r="Q29" s="40" t="n"/>
@@ -2587,7 +2587,7 @@
       <c r="J30" s="71" t="n"/>
       <c r="K30" s="72">
         <f>K28+K29</f>
-        <v>3930000</v>
+        <v>2810000</v>
       </c>
       <c r="L30" s="73" t="inlineStr">
         <is>
@@ -2601,19 +2601,19 @@
       </c>
       <c r="N30" s="75">
         <f>K30</f>
-        <v>3930000</v>
+        <v>2810000</v>
       </c>
       <c r="O30" s="76">
         <f>O29</f>
-        <v>3140677</v>
+        <v>2242639</v>
       </c>
       <c r="P30" s="77">
         <f>N30-O30</f>
-        <v>789323</v>
+        <v>567361</v>
       </c>
       <c r="Q30" s="78">
         <f>IF(N30=0,"",P30/N30)</f>
-        <v>0.20084554707379135</v>
+        <v>0.20190782918149466</v>
       </c>
     </row>
     <row r="31" ht="8" customHeight="1"/>
@@ -2638,7 +2638,7 @@
     <row r="33">
       <c r="A33" s="81" t="str">
         <f>"【法定福利費相当額（Ａ）】"&amp;TEXT('法定福利費内訳明細書'!$F$28,"#,##0")&amp;"円　　Ａ＝Ｙ×Ｚ　Ｙ：労務費相当額 "&amp;TEXT('法定福利費内訳明細書'!$C$17,"#,##0")&amp;"円　Ｚ：法定福利費事業者負担率（合計値："&amp;TEXT('法定福利費内訳明細書'!$E$28*100,"0.000")&amp;"／100）"</f>
-        <v>【法定福利費相当額（Ａ）】159,088円　　Ａ＝Ｙ×Ｚ　Ｙ：労務費相当額 971,545円　Ｚ：法定福利費事業者負担率（合計値：16.375／100）</v>
+        <v>【法定福利費相当額（Ａ）】164,469円　　Ａ＝Ｙ×Ｚ　Ｙ：労務費相当額 1,004,413円　Ｚ：法定福利費事業者負担率（合計値：16.375／100）</v>
       </c>
       <c r="B33" s="4" t="n"/>
       <c r="C33" s="4" t="n"/>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="N35" s="86">
         <f>IF(INCLUDE_TBD=1,SUBMIT,ROUNDUP((COST_TOTAL+N34)/(1-TARGET_MARGIN)/ROUND_UNIT,0)*ROUND_UNIT)</f>
-        <v>3930000</v>
+        <v>2810000</v>
       </c>
       <c r="O35" s="47" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M36" s="85" t="inlineStr">
         <is>
-          <t>単価要確認 28件：AC-1 床置形ペア EcoZEAS・AC-2 壁掛形・AC-3 壁掛形・室外機置台・スリーブインサート費・EF-1 パイプ用ファン・EF-2 天井埋込形換気扇・EF-3 天井埋込形換気扇・EF-4 天井埋込形換気扇・SA-1 給排気グリル・SA-2 給排気グリル・SA-3 給排気グリル・深形フード・深形フード・深形フード・パイプ用ファン取付・天井埋込形換気扇取付・天井埋込形換気扇取付・給排気グリル取付・屋外フード取付・スパイラルダクト・スパイラルダクト・スパイラルダクト・ダクト保温・外壁貫通処理・外壁貫通処理・外壁貫通処理・試運転調整費</t>
+          <t>単価要確認 15件：室外機置台・スリーブインサート費・パイプ用ファン取付・天井埋込形換気扇取付・天井埋込形換気扇取付・給排気グリル取付・屋外フード取付・スパイラルダクト・スパイラルダクト・スパイラルダクト・ダクト保温・外壁貫通処理・外壁貫通処理・外壁貫通処理・試運転調整費</t>
         </is>
       </c>
       <c r="N36" s="86" t="n"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="M38" s="85" t="inlineStr">
         <is>
-          <t>機器の提出率 0.60・仕入率 0.45 は想定（実際の仕入値で job.py の EQ_COST を更新）</t>
+          <t>機器の仕入率はダイキン業務用0.20・家庭用0.30・三菱電機換気0.32（job.py の EQ_RATES）。目標粗利率を変えた場合は機器の提出単価も job.py で再生成</t>
         </is>
       </c>
       <c r="N38" s="86" t="n"/>
@@ -2860,16 +2860,16 @@
       </c>
       <c r="N44" s="86">
         <f>K30</f>
-        <v>3930000</v>
+        <v>2810000</v>
       </c>
       <c r="O44" s="86">
         <f>COST_TOTAL+'内訳書(空調設備工事)'!M104*(N47-LABOR_COST)*(1+WELFARE_RATE)</f>
-        <v>3395431.766875</v>
+        <v>2497393.766875</v>
       </c>
       <c r="P44" s="40" t="n"/>
       <c r="Q44" s="49">
         <f>(N44-O44)/N44</f>
-        <v>0.13602245117684472</v>
+        <v>0.1112477697953736</v>
       </c>
     </row>
     <row r="45">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="N45" s="49">
         <f>IF(K28=0,"",-K29/K28)</f>
-        <v>0.058290161648207876</v>
+        <v>0.026431855426862858</v>
       </c>
       <c r="O45" s="40" t="n"/>
       <c r="P45" s="40" t="n"/>
@@ -2936,11 +2936,11 @@
       </c>
       <c r="N50" s="43">
         <f>ROUNDUP(COST_TOTAL/(1-M50),-4)</f>
-        <v>3490000</v>
+        <v>2500000</v>
       </c>
       <c r="O50" s="100">
         <f>IF(K28=0,"",1-N50/K28)</f>
-        <v>0.16372332421176727</v>
+        <v>0.13383617030859685</v>
       </c>
     </row>
     <row r="51">
@@ -2949,11 +2949,11 @@
       </c>
       <c r="N51" s="43">
         <f>ROUNDUP(COST_TOTAL/(1-M51),-4)</f>
-        <v>3700000</v>
+        <v>2640000</v>
       </c>
       <c r="O51" s="100">
         <f>IF(K28=0,"",1-N51/K28)</f>
-        <v>0.11340295117006849</v>
+        <v>0.08533099584587822</v>
       </c>
     </row>
     <row r="52">
@@ -2962,11 +2962,11 @@
       </c>
       <c r="N52" s="43">
         <f>ROUNDUP(COST_TOTAL/(1-M52),-4)</f>
-        <v>3930000</v>
+        <v>2810000</v>
       </c>
       <c r="O52" s="100">
         <f>IF(K28=0,"",1-N52/K28)</f>
-        <v>0.05829016164820788</v>
+        <v>0.026431855426862882</v>
       </c>
     </row>
     <row r="53">
@@ -2975,11 +2975,11 @@
       </c>
       <c r="N53" s="43">
         <f>ROUNDUP(COST_TOTAL/(1-M53),-4)</f>
-        <v>4190000</v>
+        <v>3000000</v>
       </c>
       <c r="O53" s="100">
         <f>IF(K28=0,"",1-N53/K28)</f>
-        <v>-0.0040112525938953425</v>
+        <v>-0.039396595629683784</v>
       </c>
     </row>
     <row r="54">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="N54" s="43">
         <f>ROUNDUP(COST_TOTAL/(1-M54),-4)</f>
-        <v>4490000</v>
+        <v>3210000</v>
       </c>
       <c r="O54" s="100">
         <f>IF(K28=0,"",1-N54/K28)</f>
-        <v>-0.07589749979632221</v>
+        <v>-0.11215435732376156</v>
       </c>
     </row>
   </sheetData>
@@ -3378,11 +3378,11 @@
         </is>
       </c>
       <c r="G7" s="116" t="n">
-        <v>759600</v>
+        <v>316500</v>
       </c>
       <c r="H7" s="118">
         <f>ROUND(E7*G7,0)</f>
-        <v>1519200</v>
+        <v>633000</v>
       </c>
       <c r="I7" s="119" t="inlineStr">
         <is>
@@ -3391,17 +3391,12 @@
       </c>
       <c r="J7" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K7" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L7" s="116">
-        <f>ROUND(G7*MAT_RATIO*0.75,0)</f>
-        <v>569700</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K7" s="120" t="n"/>
+      <c r="L7" s="121" t="n">
+        <v>253200</v>
       </c>
       <c r="M7" s="122" t="n">
         <v>0</v>
@@ -3412,11 +3407,11 @@
       </c>
       <c r="O7" s="116">
         <f>L7+N7</f>
-        <v>569700</v>
+        <v>253200</v>
       </c>
       <c r="P7" s="118">
         <f>E7*O7</f>
-        <v>1139400</v>
+        <v>506400</v>
       </c>
       <c r="Q7" s="118">
         <f>E7*N7</f>
@@ -3428,17 +3423,17 @@
       </c>
       <c r="S7" s="118">
         <f>IF(H7="","",H7-P7)</f>
-        <v>379800</v>
+        <v>126600</v>
       </c>
       <c r="T7" s="123">
         <f>IF(OR(H7="",H7=0),"",S7/H7)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U7" s="40" t="n"/>
       <c r="V7" s="40" t="n"/>
       <c r="W7" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 1,266,000円 × 提出率 0.60（VE案 8月10日付 定価）</t>
+          <t>原価基準: 定価 1,266,000円（VE案 8月10日付 定価）× 仕入率 0.20（ダイキン業務用（EcoZEAS・FIVESTAR））＝原価 253,200円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X7" s="124" t="n"/>
@@ -3449,7 +3444,7 @@
       </c>
       <c r="Z7" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 1,266,000円・仕入率 0.45 想定</t>
+          <t>定価 1,266,000円 × 仕入率 0.20（ダイキン業務用（EcoZEAS・FIVESTAR））＝原価 253,200円</t>
         </is>
       </c>
     </row>
@@ -3507,11 +3502,11 @@
         </is>
       </c>
       <c r="G9" s="116" t="n">
-        <v>228000</v>
+        <v>142500</v>
       </c>
       <c r="H9" s="118">
         <f>ROUND(E9*G9,0)</f>
-        <v>456000</v>
+        <v>285000</v>
       </c>
       <c r="I9" s="119" t="inlineStr">
         <is>
@@ -3520,17 +3515,12 @@
       </c>
       <c r="J9" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K9" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L9" s="116">
-        <f>ROUND(G9*MAT_RATIO*0.75,0)</f>
-        <v>171000</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K9" s="120" t="n"/>
+      <c r="L9" s="121" t="n">
+        <v>114000</v>
       </c>
       <c r="M9" s="122" t="n">
         <v>0</v>
@@ -3541,11 +3531,11 @@
       </c>
       <c r="O9" s="116">
         <f>L9+N9</f>
-        <v>171000</v>
+        <v>114000</v>
       </c>
       <c r="P9" s="118">
         <f>E9*O9</f>
-        <v>342000</v>
+        <v>228000</v>
       </c>
       <c r="Q9" s="118">
         <f>E9*N9</f>
@@ -3557,17 +3547,17 @@
       </c>
       <c r="S9" s="118">
         <f>IF(H9="","",H9-P9)</f>
-        <v>114000</v>
+        <v>57000</v>
       </c>
       <c r="T9" s="123">
         <f>IF(OR(H9="",H9=0),"",S9/H9)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U9" s="40" t="n"/>
       <c r="V9" s="40" t="n"/>
       <c r="W9" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 380,000円 × 提出率 0.60（VE案 8月10日付 定価）</t>
+          <t>原価基準: 定価 380,000円（VE案 8月10日付 定価）× 仕入率 0.30（ダイキン家庭用（定価あり））＝原価 114,000円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X9" s="124" t="n"/>
@@ -3578,7 +3568,7 @@
       </c>
       <c r="Z9" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 380,000円・仕入率 0.45 想定</t>
+          <t>定価 380,000円 × 仕入率 0.30（ダイキン家庭用（定価あり））＝原価 114,000円</t>
         </is>
       </c>
     </row>
@@ -3604,11 +3594,11 @@
         </is>
       </c>
       <c r="G10" s="127" t="n">
-        <v>270000</v>
+        <v>168750</v>
       </c>
       <c r="H10" s="129">
         <f>ROUND(E10*G10,0)</f>
-        <v>270000</v>
+        <v>168750</v>
       </c>
       <c r="I10" s="130" t="inlineStr">
         <is>
@@ -3617,17 +3607,12 @@
       </c>
       <c r="J10" s="131" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K10" s="132" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L10" s="127">
-        <f>ROUND(G10*MAT_RATIO*0.75,0)</f>
-        <v>202500</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K10" s="131" t="n"/>
+      <c r="L10" s="132" t="n">
+        <v>135000</v>
       </c>
       <c r="M10" s="133" t="n">
         <v>0</v>
@@ -3638,11 +3623,11 @@
       </c>
       <c r="O10" s="127">
         <f>L10+N10</f>
-        <v>202500</v>
+        <v>135000</v>
       </c>
       <c r="P10" s="129">
         <f>E10*O10</f>
-        <v>202500</v>
+        <v>135000</v>
       </c>
       <c r="Q10" s="129">
         <f>E10*N10</f>
@@ -3654,17 +3639,17 @@
       </c>
       <c r="S10" s="129">
         <f>IF(H10="","",H10-P10)</f>
-        <v>67500</v>
+        <v>33750</v>
       </c>
       <c r="T10" s="134">
         <f>IF(OR(H10="",H10=0),"",S10/H10)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U10" s="91" t="n"/>
       <c r="V10" s="91" t="n"/>
       <c r="W10" s="135" t="inlineStr">
         <is>
-          <t>推定: 定価 450,000円 × 提出率 0.60（VE案 8月10日付 定価）</t>
+          <t>原価基準: 定価 450,000円（VE案 8月10日付 定価）× 仕入率 0.30（ダイキン家庭用（定価あり））＝原価 135,000円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X10" s="135" t="n"/>
@@ -3675,7 +3660,7 @@
       </c>
       <c r="Z10" s="135" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 450,000円・仕入率 0.45 想定</t>
+          <t>定価 450,000円 × 仕入率 0.30（ダイキン家庭用（定価あり））＝原価 135,000円</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3678,7 @@
       <c r="G11" s="109" t="n"/>
       <c r="H11" s="137">
         <f>SUM(H6:H10)</f>
-        <v>2245200</v>
+        <v>1086750</v>
       </c>
       <c r="I11" s="110" t="n"/>
       <c r="J11" s="109" t="n"/>
@@ -3707,7 +3692,7 @@
       <c r="O11" s="109" t="n"/>
       <c r="P11" s="137">
         <f>SUM(P6:P10)</f>
-        <v>1683900</v>
+        <v>869400</v>
       </c>
       <c r="Q11" s="137">
         <f>SUM(Q6:Q10)</f>
@@ -3719,11 +3704,11 @@
       </c>
       <c r="S11" s="137">
         <f>H11-P11</f>
-        <v>561300</v>
+        <v>217350</v>
       </c>
       <c r="T11" s="139">
         <f>IF(H11=0,"",S11/H11)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U11" s="109" t="n"/>
       <c r="V11" s="109" t="n"/>
@@ -3863,7 +3848,7 @@
         </is>
       </c>
       <c r="K15" s="120" t="n"/>
-      <c r="L15" s="141" t="n">
+      <c r="L15" s="121" t="n">
         <v>1500</v>
       </c>
       <c r="M15" s="122" t="n">
@@ -3959,7 +3944,7 @@
         </is>
       </c>
       <c r="K16" s="120" t="n"/>
-      <c r="L16" s="141" t="n">
+      <c r="L16" s="121" t="n">
         <v>1500</v>
       </c>
       <c r="M16" s="122" t="n">
@@ -4055,7 +4040,7 @@
         </is>
       </c>
       <c r="K17" s="120" t="n"/>
-      <c r="L17" s="141" t="n">
+      <c r="L17" s="121" t="n">
         <v>500</v>
       </c>
       <c r="M17" s="122" t="n">
@@ -4147,7 +4132,7 @@
         </is>
       </c>
       <c r="K18" s="120" t="n"/>
-      <c r="L18" s="141" t="n">
+      <c r="L18" s="121" t="n">
         <v>800</v>
       </c>
       <c r="M18" s="122" t="n">
@@ -4271,7 +4256,7 @@
         </is>
       </c>
       <c r="K20" s="120" t="n"/>
-      <c r="L20" s="141" t="n">
+      <c r="L20" s="121" t="n">
         <v>2500</v>
       </c>
       <c r="M20" s="122" t="n">
@@ -4335,7 +4320,7 @@
         </is>
       </c>
       <c r="B21" s="40" t="n"/>
-      <c r="C21" s="142" t="inlineStr">
+      <c r="C21" s="141" t="inlineStr">
         <is>
           <t>RA 室外機用 プラ製（防振ゴム付）</t>
         </is>
@@ -4366,12 +4351,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K21" s="121" t="inlineStr">
+      <c r="K21" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L21" s="141" t="n">
+      <c r="L21" s="121" t="n">
         <v>2500</v>
       </c>
       <c r="M21" s="122" t="n">
@@ -4491,7 +4476,7 @@
         </is>
       </c>
       <c r="K23" s="120" t="n"/>
-      <c r="L23" s="141" t="n">
+      <c r="L23" s="121" t="n">
         <v>450</v>
       </c>
       <c r="M23" s="122" t="n">
@@ -4575,7 +4560,7 @@
         </is>
       </c>
       <c r="K24" s="120" t="n"/>
-      <c r="L24" s="141" t="n">
+      <c r="L24" s="121" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="122" t="n">
@@ -5046,7 +5031,7 @@
         </is>
       </c>
       <c r="B33" s="40" t="n"/>
-      <c r="C33" s="142" t="inlineStr">
+      <c r="C33" s="141" t="inlineStr">
         <is>
           <t>6.35+9.52mm（10t+20t）AC-2・AC-3</t>
         </is>
@@ -6076,7 +6061,7 @@
         </is>
       </c>
       <c r="K48" s="120" t="n"/>
-      <c r="L48" s="141" t="n">
+      <c r="L48" s="121" t="n">
         <v>2400</v>
       </c>
       <c r="M48" s="122" t="n">
@@ -6172,7 +6157,7 @@
         </is>
       </c>
       <c r="K49" s="120" t="n"/>
-      <c r="L49" s="141" t="n">
+      <c r="L49" s="121" t="n">
         <v>1800</v>
       </c>
       <c r="M49" s="122" t="n">
@@ -6268,7 +6253,7 @@
         </is>
       </c>
       <c r="K50" s="120" t="n"/>
-      <c r="L50" s="141" t="n">
+      <c r="L50" s="121" t="n">
         <v>900</v>
       </c>
       <c r="M50" s="122" t="n">
@@ -6387,12 +6372,12 @@
           <t>推定（要確認）</t>
         </is>
       </c>
-      <c r="K52" s="121" t="inlineStr">
+      <c r="K52" s="142" t="inlineStr">
         <is>
           <t>単価要確認（推定）</t>
         </is>
       </c>
-      <c r="L52" s="141" t="n">
+      <c r="L52" s="121" t="n">
         <v>1500</v>
       </c>
       <c r="M52" s="122" t="n">
@@ -6480,7 +6465,7 @@
         </is>
       </c>
       <c r="K53" s="120" t="n"/>
-      <c r="L53" s="141" t="n">
+      <c r="L53" s="121" t="n">
         <v>2000</v>
       </c>
       <c r="M53" s="122" t="n">
@@ -6564,7 +6549,7 @@
         </is>
       </c>
       <c r="K54" s="120" t="n"/>
-      <c r="L54" s="141" t="n">
+      <c r="L54" s="121" t="n">
         <v>1000</v>
       </c>
       <c r="M54" s="122" t="n">
@@ -6648,7 +6633,7 @@
         </is>
       </c>
       <c r="K55" s="120" t="n"/>
-      <c r="L55" s="141" t="n">
+      <c r="L55" s="121" t="n">
         <v>500</v>
       </c>
       <c r="M55" s="122" t="n">
@@ -6736,7 +6721,7 @@
         </is>
       </c>
       <c r="K56" s="120" t="n"/>
-      <c r="L56" s="141" t="n">
+      <c r="L56" s="121" t="n">
         <v>300</v>
       </c>
       <c r="M56" s="122" t="n">
@@ -7123,11 +7108,11 @@
         </is>
       </c>
       <c r="G64" s="116" t="n">
-        <v>7380</v>
+        <v>4920</v>
       </c>
       <c r="H64" s="118">
         <f>ROUND(E64*G64,0)</f>
-        <v>22140</v>
+        <v>14760</v>
       </c>
       <c r="I64" s="119" t="inlineStr">
         <is>
@@ -7136,17 +7121,12 @@
       </c>
       <c r="J64" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K64" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L64" s="116">
-        <f>ROUND(G64*MAT_RATIO*0.75,0)</f>
-        <v>5535</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K64" s="120" t="n"/>
+      <c r="L64" s="121" t="n">
+        <v>3936</v>
       </c>
       <c r="M64" s="122" t="n">
         <v>0</v>
@@ -7157,11 +7137,11 @@
       </c>
       <c r="O64" s="116">
         <f>L64+N64</f>
-        <v>5535</v>
+        <v>3936</v>
       </c>
       <c r="P64" s="118">
         <f>E64*O64</f>
-        <v>16605</v>
+        <v>11808</v>
       </c>
       <c r="Q64" s="118">
         <f>E64*N64</f>
@@ -7173,17 +7153,17 @@
       </c>
       <c r="S64" s="118">
         <f>IF(H64="","",H64-P64)</f>
-        <v>5535</v>
+        <v>2952</v>
       </c>
       <c r="T64" s="123">
         <f>IF(OR(H64="",H64=0),"",S64/H64)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U64" s="40" t="n"/>
       <c r="V64" s="40" t="n"/>
       <c r="W64" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 12,300円 × 提出率 0.60（三菱電機 WIN2K 価格（税別））</t>
+          <t>原価基準: 定価 12,300円（三菱電機 WIN2K 価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 3,936円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X64" s="124" t="n"/>
@@ -7194,7 +7174,7 @@
       </c>
       <c r="Z64" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 12,300円・仕入率 0.45 想定</t>
+          <t>定価 12,300円 × 仕入率 0.32（三菱電機 換気機器）＝原価 3,936円</t>
         </is>
       </c>
     </row>
@@ -7252,11 +7232,11 @@
         </is>
       </c>
       <c r="G66" s="116" t="n">
-        <v>23880</v>
+        <v>15920</v>
       </c>
       <c r="H66" s="118">
         <f>ROUND(E66*G66,0)</f>
-        <v>119400</v>
+        <v>79600</v>
       </c>
       <c r="I66" s="119" t="inlineStr">
         <is>
@@ -7265,17 +7245,12 @@
       </c>
       <c r="J66" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K66" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L66" s="116">
-        <f>ROUND(G66*MAT_RATIO*0.75,0)</f>
-        <v>17910</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K66" s="120" t="n"/>
+      <c r="L66" s="121" t="n">
+        <v>12736</v>
       </c>
       <c r="M66" s="122" t="n">
         <v>0</v>
@@ -7286,11 +7261,11 @@
       </c>
       <c r="O66" s="116">
         <f>L66+N66</f>
-        <v>17910</v>
+        <v>12736</v>
       </c>
       <c r="P66" s="118">
         <f>E66*O66</f>
-        <v>89550</v>
+        <v>63680</v>
       </c>
       <c r="Q66" s="118">
         <f>E66*N66</f>
@@ -7302,17 +7277,17 @@
       </c>
       <c r="S66" s="118">
         <f>IF(H66="","",H66-P66)</f>
-        <v>29850</v>
+        <v>15920</v>
       </c>
       <c r="T66" s="123">
         <f>IF(OR(H66="",H66=0),"",S66/H66)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U66" s="40" t="n"/>
       <c r="V66" s="40" t="n"/>
       <c r="W66" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 39,800円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 39,800円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 12,736円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X66" s="124" t="n"/>
@@ -7323,7 +7298,7 @@
       </c>
       <c r="Z66" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 39,800円・仕入率 0.45 想定</t>
+          <t>定価 39,800円 × 仕入率 0.32（三菱電機 換気機器）＝原価 12,736円</t>
         </is>
       </c>
     </row>
@@ -7349,11 +7324,11 @@
         </is>
       </c>
       <c r="G67" s="116" t="n">
-        <v>15120</v>
+        <v>10080</v>
       </c>
       <c r="H67" s="118">
         <f>ROUND(E67*G67,0)</f>
-        <v>15120</v>
+        <v>10080</v>
       </c>
       <c r="I67" s="119" t="inlineStr">
         <is>
@@ -7362,17 +7337,12 @@
       </c>
       <c r="J67" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K67" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L67" s="116">
-        <f>ROUND(G67*MAT_RATIO*0.75,0)</f>
-        <v>11340</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K67" s="120" t="n"/>
+      <c r="L67" s="121" t="n">
+        <v>8064</v>
       </c>
       <c r="M67" s="122" t="n">
         <v>0</v>
@@ -7383,11 +7353,11 @@
       </c>
       <c r="O67" s="116">
         <f>L67+N67</f>
-        <v>11340</v>
+        <v>8064</v>
       </c>
       <c r="P67" s="118">
         <f>E67*O67</f>
-        <v>11340</v>
+        <v>8064</v>
       </c>
       <c r="Q67" s="118">
         <f>E67*N67</f>
@@ -7399,17 +7369,17 @@
       </c>
       <c r="S67" s="118">
         <f>IF(H67="","",H67-P67)</f>
-        <v>3780</v>
+        <v>2016</v>
       </c>
       <c r="T67" s="123">
         <f>IF(OR(H67="",H67=0),"",S67/H67)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U67" s="40" t="n"/>
       <c r="V67" s="40" t="n"/>
       <c r="W67" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 25,200円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 25,200円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 8,064円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X67" s="124" t="n"/>
@@ -7420,7 +7390,7 @@
       </c>
       <c r="Z67" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 25,200円・仕入率 0.45 想定</t>
+          <t>定価 25,200円 × 仕入率 0.32（三菱電機 換気機器）＝原価 8,064円</t>
         </is>
       </c>
     </row>
@@ -7446,11 +7416,11 @@
         </is>
       </c>
       <c r="G68" s="116" t="n">
-        <v>12420</v>
+        <v>8280</v>
       </c>
       <c r="H68" s="118">
         <f>ROUND(E68*G68,0)</f>
-        <v>12420</v>
+        <v>8280</v>
       </c>
       <c r="I68" s="119" t="inlineStr">
         <is>
@@ -7459,17 +7429,12 @@
       </c>
       <c r="J68" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K68" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L68" s="116">
-        <f>ROUND(G68*MAT_RATIO*0.75,0)</f>
-        <v>9315</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K68" s="120" t="n"/>
+      <c r="L68" s="121" t="n">
+        <v>6624</v>
       </c>
       <c r="M68" s="122" t="n">
         <v>0</v>
@@ -7480,11 +7445,11 @@
       </c>
       <c r="O68" s="116">
         <f>L68+N68</f>
-        <v>9315</v>
+        <v>6624</v>
       </c>
       <c r="P68" s="118">
         <f>E68*O68</f>
-        <v>9315</v>
+        <v>6624</v>
       </c>
       <c r="Q68" s="118">
         <f>E68*N68</f>
@@ -7496,17 +7461,17 @@
       </c>
       <c r="S68" s="118">
         <f>IF(H68="","",H68-P68)</f>
-        <v>3105</v>
+        <v>1656</v>
       </c>
       <c r="T68" s="123">
         <f>IF(OR(H68="",H68=0),"",S68/H68)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U68" s="40" t="n"/>
       <c r="V68" s="40" t="n"/>
       <c r="W68" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 20,700円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 20,700円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 6,624円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X68" s="124" t="n"/>
@@ -7517,7 +7482,7 @@
       </c>
       <c r="Z68" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 20,700円・仕入率 0.45 想定</t>
+          <t>定価 20,700円 × 仕入率 0.32（三菱電機 換気機器）＝原価 6,624円</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7525,7 @@
         </is>
       </c>
       <c r="B70" s="40" t="n"/>
-      <c r="C70" s="142" t="inlineStr">
+      <c r="C70" s="141" t="inlineStr">
         <is>
           <t>P-23GHF5（三菱）φ200 フィルター付</t>
         </is>
@@ -7575,11 +7540,11 @@
         </is>
       </c>
       <c r="G70" s="116" t="n">
-        <v>6540</v>
+        <v>4360</v>
       </c>
       <c r="H70" s="118">
         <f>ROUND(E70*G70,0)</f>
-        <v>26160</v>
+        <v>17440</v>
       </c>
       <c r="I70" s="119" t="inlineStr">
         <is>
@@ -7588,17 +7553,12 @@
       </c>
       <c r="J70" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K70" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L70" s="116">
-        <f>ROUND(G70*MAT_RATIO*0.75,0)</f>
-        <v>4905</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K70" s="120" t="n"/>
+      <c r="L70" s="121" t="n">
+        <v>3488</v>
       </c>
       <c r="M70" s="122" t="n">
         <v>0</v>
@@ -7609,11 +7569,11 @@
       </c>
       <c r="O70" s="116">
         <f>L70+N70</f>
-        <v>4905</v>
+        <v>3488</v>
       </c>
       <c r="P70" s="118">
         <f>E70*O70</f>
-        <v>19620</v>
+        <v>13952</v>
       </c>
       <c r="Q70" s="118">
         <f>E70*N70</f>
@@ -7625,17 +7585,17 @@
       </c>
       <c r="S70" s="118">
         <f>IF(H70="","",H70-P70)</f>
-        <v>6540</v>
+        <v>3488</v>
       </c>
       <c r="T70" s="123">
         <f>IF(OR(H70="",H70=0),"",S70/H70)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U70" s="40" t="n"/>
       <c r="V70" s="40" t="n"/>
       <c r="W70" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 10,900円 × 提出率 0.60（三菱電機 WIN2K 価格（税別））</t>
+          <t>原価基準: 定価 10,900円（三菱電機 WIN2K 価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 3,488円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X70" s="124" t="n"/>
@@ -7646,7 +7606,7 @@
       </c>
       <c r="Z70" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 10,900円・仕入率 0.45 想定</t>
+          <t>定価 10,900円 × 仕入率 0.32（三菱電機 換気機器）＝原価 3,488円</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7617,7 @@
         </is>
       </c>
       <c r="B71" s="40" t="n"/>
-      <c r="C71" s="142" t="inlineStr">
+      <c r="C71" s="141" t="inlineStr">
         <is>
           <t>P-18GHF5（三菱）φ150 フィルター付</t>
         </is>
@@ -7672,11 +7632,11 @@
         </is>
       </c>
       <c r="G71" s="116" t="n">
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="H71" s="118">
         <f>ROUND(E71*G71,0)</f>
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="I71" s="119" t="inlineStr">
         <is>
@@ -7685,17 +7645,12 @@
       </c>
       <c r="J71" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K71" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L71" s="116">
-        <f>ROUND(G71*MAT_RATIO*0.75,0)</f>
-        <v>2700</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K71" s="120" t="n"/>
+      <c r="L71" s="121" t="n">
+        <v>1920</v>
       </c>
       <c r="M71" s="122" t="n">
         <v>0</v>
@@ -7706,11 +7661,11 @@
       </c>
       <c r="O71" s="116">
         <f>L71+N71</f>
-        <v>2700</v>
+        <v>1920</v>
       </c>
       <c r="P71" s="118">
         <f>E71*O71</f>
-        <v>2700</v>
+        <v>1920</v>
       </c>
       <c r="Q71" s="118">
         <f>E71*N71</f>
@@ -7722,17 +7677,17 @@
       </c>
       <c r="S71" s="118">
         <f>IF(H71="","",H71-P71)</f>
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="T71" s="123">
         <f>IF(OR(H71="",H71=0),"",S71/H71)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U71" s="40" t="n"/>
       <c r="V71" s="40" t="n"/>
       <c r="W71" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 6,000円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 6,000円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 1,920円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X71" s="124" t="n"/>
@@ -7743,7 +7698,7 @@
       </c>
       <c r="Z71" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 6,000円・仕入率 0.45 想定</t>
+          <t>定価 6,000円 × 仕入率 0.32（三菱電機 換気機器）＝原価 1,920円</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7709,7 @@
         </is>
       </c>
       <c r="B72" s="40" t="n"/>
-      <c r="C72" s="142" t="inlineStr">
+      <c r="C72" s="141" t="inlineStr">
         <is>
           <t>P-13GHF5（三菱）φ100 フィルター付</t>
         </is>
@@ -7769,11 +7724,11 @@
         </is>
       </c>
       <c r="G72" s="116" t="n">
-        <v>2760</v>
+        <v>1840</v>
       </c>
       <c r="H72" s="118">
         <f>ROUND(E72*G72,0)</f>
-        <v>8280</v>
+        <v>5520</v>
       </c>
       <c r="I72" s="119" t="inlineStr">
         <is>
@@ -7782,17 +7737,12 @@
       </c>
       <c r="J72" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K72" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L72" s="116">
-        <f>ROUND(G72*MAT_RATIO*0.75,0)</f>
-        <v>2070</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K72" s="120" t="n"/>
+      <c r="L72" s="121" t="n">
+        <v>1472</v>
       </c>
       <c r="M72" s="122" t="n">
         <v>0</v>
@@ -7803,11 +7753,11 @@
       </c>
       <c r="O72" s="116">
         <f>L72+N72</f>
-        <v>2070</v>
+        <v>1472</v>
       </c>
       <c r="P72" s="118">
         <f>E72*O72</f>
-        <v>6210</v>
+        <v>4416</v>
       </c>
       <c r="Q72" s="118">
         <f>E72*N72</f>
@@ -7819,17 +7769,17 @@
       </c>
       <c r="S72" s="118">
         <f>IF(H72="","",H72-P72)</f>
-        <v>2070</v>
+        <v>1104</v>
       </c>
       <c r="T72" s="123">
         <f>IF(OR(H72="",H72=0),"",S72/H72)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U72" s="40" t="n"/>
       <c r="V72" s="40" t="n"/>
       <c r="W72" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 4,600円 × 提出率 0.60（販売店掲載の参考基準価格（税別）（税込5,060円））</t>
+          <t>原価基準: 定価 4,600円（販売店掲載の参考基準価格（税別）（税込5,060円））× 仕入率 0.32（三菱電機 換気機器）＝原価 1,472円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X72" s="124" t="n"/>
@@ -7840,7 +7790,7 @@
       </c>
       <c r="Z72" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 4,600円・仕入率 0.45 想定</t>
+          <t>定価 4,600円 × 仕入率 0.32（三菱電機 換気機器）＝原価 1,472円</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7833,7 @@
         </is>
       </c>
       <c r="B74" s="40" t="n"/>
-      <c r="C74" s="142" t="inlineStr">
+      <c r="C74" s="141" t="inlineStr">
         <is>
           <t>P-13VSQ4（三菱）φ100 SUS 防虫網付</t>
         </is>
@@ -7898,11 +7848,11 @@
         </is>
       </c>
       <c r="G74" s="116" t="n">
-        <v>6300</v>
+        <v>4200</v>
       </c>
       <c r="H74" s="118">
         <f>ROUND(E74*G74,0)</f>
-        <v>50400</v>
+        <v>33600</v>
       </c>
       <c r="I74" s="119" t="inlineStr">
         <is>
@@ -7911,17 +7861,12 @@
       </c>
       <c r="J74" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K74" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L74" s="116">
-        <f>ROUND(G74*MAT_RATIO*0.75,0)</f>
-        <v>4725</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K74" s="120" t="n"/>
+      <c r="L74" s="121" t="n">
+        <v>3360</v>
       </c>
       <c r="M74" s="122" t="n">
         <v>0</v>
@@ -7932,11 +7877,11 @@
       </c>
       <c r="O74" s="116">
         <f>L74+N74</f>
-        <v>4725</v>
+        <v>3360</v>
       </c>
       <c r="P74" s="118">
         <f>E74*O74</f>
-        <v>37800</v>
+        <v>26880</v>
       </c>
       <c r="Q74" s="118">
         <f>E74*N74</f>
@@ -7948,17 +7893,17 @@
       </c>
       <c r="S74" s="118">
         <f>IF(H74="","",H74-P74)</f>
-        <v>12600</v>
+        <v>6720</v>
       </c>
       <c r="T74" s="123">
         <f>IF(OR(H74="",H74=0),"",S74/H74)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U74" s="40" t="n"/>
       <c r="V74" s="40" t="n"/>
       <c r="W74" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 10,500円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 10,500円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 3,360円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X74" s="124" t="n"/>
@@ -7969,7 +7914,7 @@
       </c>
       <c r="Z74" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 10,500円・仕入率 0.45 想定</t>
+          <t>定価 10,500円 × 仕入率 0.32（三菱電機 換気機器）＝原価 3,360円</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7925,7 @@
         </is>
       </c>
       <c r="B75" s="40" t="n"/>
-      <c r="C75" s="142" t="inlineStr">
+      <c r="C75" s="141" t="inlineStr">
         <is>
           <t>P-18VSQ4（三菱）φ150 SUS 防虫網付</t>
         </is>
@@ -7995,11 +7940,11 @@
         </is>
       </c>
       <c r="G75" s="116" t="n">
-        <v>7980</v>
+        <v>5320</v>
       </c>
       <c r="H75" s="118">
         <f>ROUND(E75*G75,0)</f>
-        <v>47880</v>
+        <v>31920</v>
       </c>
       <c r="I75" s="119" t="inlineStr">
         <is>
@@ -8008,17 +7953,12 @@
       </c>
       <c r="J75" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K75" s="121" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L75" s="116">
-        <f>ROUND(G75*MAT_RATIO*0.75,0)</f>
-        <v>5985</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K75" s="120" t="n"/>
+      <c r="L75" s="121" t="n">
+        <v>4256</v>
       </c>
       <c r="M75" s="122" t="n">
         <v>0</v>
@@ -8029,11 +7969,11 @@
       </c>
       <c r="O75" s="116">
         <f>L75+N75</f>
-        <v>5985</v>
+        <v>4256</v>
       </c>
       <c r="P75" s="118">
         <f>E75*O75</f>
-        <v>35910</v>
+        <v>25536</v>
       </c>
       <c r="Q75" s="118">
         <f>E75*N75</f>
@@ -8045,17 +7985,17 @@
       </c>
       <c r="S75" s="118">
         <f>IF(H75="","",H75-P75)</f>
-        <v>11970</v>
+        <v>6384</v>
       </c>
       <c r="T75" s="123">
         <f>IF(OR(H75="",H75=0),"",S75/H75)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U75" s="40" t="n"/>
       <c r="V75" s="40" t="n"/>
       <c r="W75" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 13,300円 × 提出率 0.60（三菱電機 WIN2K 価格（税別））</t>
+          <t>原価基準: 定価 13,300円（三菱電機 WIN2K 価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 4,256円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X75" s="124" t="n"/>
@@ -8066,7 +8006,7 @@
       </c>
       <c r="Z75" s="124" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 13,300円・仕入率 0.45 想定</t>
+          <t>定価 13,300円 × 仕入率 0.32（三菱電機 換気機器）＝原価 4,256円</t>
         </is>
       </c>
     </row>
@@ -8092,11 +8032,11 @@
         </is>
       </c>
       <c r="G76" s="127" t="n">
-        <v>20040</v>
+        <v>13360</v>
       </c>
       <c r="H76" s="129">
         <f>ROUND(E76*G76,0)</f>
-        <v>80160</v>
+        <v>53440</v>
       </c>
       <c r="I76" s="130" t="inlineStr">
         <is>
@@ -8105,17 +8045,12 @@
       </c>
       <c r="J76" s="131" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="K76" s="132" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
-      <c r="L76" s="127">
-        <f>ROUND(G76*MAT_RATIO*0.75,0)</f>
-        <v>15030</v>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="K76" s="131" t="n"/>
+      <c r="L76" s="132" t="n">
+        <v>10688</v>
       </c>
       <c r="M76" s="133" t="n">
         <v>0</v>
@@ -8126,11 +8061,11 @@
       </c>
       <c r="O76" s="127">
         <f>L76+N76</f>
-        <v>15030</v>
+        <v>10688</v>
       </c>
       <c r="P76" s="129">
         <f>E76*O76</f>
-        <v>60120</v>
+        <v>42752</v>
       </c>
       <c r="Q76" s="129">
         <f>E76*N76</f>
@@ -8142,17 +8077,17 @@
       </c>
       <c r="S76" s="129">
         <f>IF(H76="","",H76-P76)</f>
-        <v>20040</v>
+        <v>10688</v>
       </c>
       <c r="T76" s="134">
         <f>IF(OR(H76="",H76=0),"",S76/H76)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U76" s="91" t="n"/>
       <c r="V76" s="91" t="n"/>
       <c r="W76" s="135" t="inlineStr">
         <is>
-          <t>推定: 定価 33,400円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 33,400円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 10,688円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
       <c r="X76" s="135" t="n"/>
@@ -8163,7 +8098,7 @@
       </c>
       <c r="Z76" s="135" t="inlineStr">
         <is>
-          <t>機器原価＝提出単価×材料原価率×0.75（仕入率÷提出率）｜定価 33,400円・仕入率 0.45 想定</t>
+          <t>定価 33,400円 × 仕入率 0.32（三菱電機 換気機器）＝原価 10,688円</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8116,7 @@
       <c r="G77" s="109" t="n"/>
       <c r="H77" s="137">
         <f>SUM(H63:H76)</f>
-        <v>385560</v>
+        <v>257040</v>
       </c>
       <c r="I77" s="110" t="n"/>
       <c r="J77" s="109" t="n"/>
@@ -8195,7 +8130,7 @@
       <c r="O77" s="109" t="n"/>
       <c r="P77" s="137">
         <f>SUM(P63:P76)</f>
-        <v>289170</v>
+        <v>205632</v>
       </c>
       <c r="Q77" s="137">
         <f>SUM(Q63:Q76)</f>
@@ -8207,11 +8142,11 @@
       </c>
       <c r="S77" s="137">
         <f>H77-P77</f>
-        <v>96390</v>
+        <v>51408</v>
       </c>
       <c r="T77" s="139">
         <f>IF(H77=0,"",S77/H77)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U77" s="109" t="n"/>
       <c r="V77" s="109" t="n"/>
@@ -8350,12 +8285,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K81" s="121" t="inlineStr">
+      <c r="K81" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L81" s="141" t="n">
+      <c r="L81" s="121" t="n">
         <v>800</v>
       </c>
       <c r="M81" s="122" t="n">
@@ -8446,12 +8381,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K82" s="121" t="inlineStr">
+      <c r="K82" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L82" s="141" t="n">
+      <c r="L82" s="121" t="n">
         <v>800</v>
       </c>
       <c r="M82" s="122" t="n">
@@ -8542,12 +8477,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K83" s="121" t="inlineStr">
+      <c r="K83" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L83" s="141" t="n">
+      <c r="L83" s="121" t="n">
         <v>500</v>
       </c>
       <c r="M83" s="122" t="n">
@@ -8634,12 +8569,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K84" s="121" t="inlineStr">
+      <c r="K84" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L84" s="141" t="n">
+      <c r="L84" s="121" t="n">
         <v>300</v>
       </c>
       <c r="M84" s="122" t="n">
@@ -8726,12 +8661,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K85" s="121" t="inlineStr">
+      <c r="K85" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L85" s="141" t="n">
+      <c r="L85" s="121" t="n">
         <v>300</v>
       </c>
       <c r="M85" s="122" t="n">
@@ -8854,12 +8789,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K87" s="121" t="inlineStr">
+      <c r="K87" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L87" s="141" t="n">
+      <c r="L87" s="121" t="n">
         <v>1000</v>
       </c>
       <c r="M87" s="122" t="n">
@@ -8954,12 +8889,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K88" s="121" t="inlineStr">
+      <c r="K88" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L88" s="141" t="n">
+      <c r="L88" s="121" t="n">
         <v>1400</v>
       </c>
       <c r="M88" s="122" t="n">
@@ -9054,12 +8989,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K89" s="121" t="inlineStr">
+      <c r="K89" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L89" s="141" t="n">
+      <c r="L89" s="121" t="n">
         <v>1900</v>
       </c>
       <c r="M89" s="122" t="n">
@@ -9154,12 +9089,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K90" s="121" t="inlineStr">
+      <c r="K90" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L90" s="141" t="n">
+      <c r="L90" s="121" t="n">
         <v>1100</v>
       </c>
       <c r="M90" s="122" t="n">
@@ -9282,12 +9217,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K92" s="121" t="inlineStr">
+      <c r="K92" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L92" s="141" t="n">
+      <c r="L92" s="121" t="n">
         <v>800</v>
       </c>
       <c r="M92" s="122" t="n">
@@ -9378,12 +9313,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K93" s="121" t="inlineStr">
+      <c r="K93" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L93" s="141" t="n">
+      <c r="L93" s="121" t="n">
         <v>1000</v>
       </c>
       <c r="M93" s="122" t="n">
@@ -9470,12 +9405,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K94" s="121" t="inlineStr">
+      <c r="K94" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L94" s="141" t="n">
+      <c r="L94" s="121" t="n">
         <v>1200</v>
       </c>
       <c r="M94" s="122" t="n">
@@ -9594,12 +9529,12 @@
           <t>当社単価（要確認）</t>
         </is>
       </c>
-      <c r="K96" s="121" t="inlineStr">
+      <c r="K96" s="142" t="inlineStr">
         <is>
           <t>単価要確認</t>
         </is>
       </c>
-      <c r="L96" s="141" t="n">
+      <c r="L96" s="121" t="n">
         <v>3000</v>
       </c>
       <c r="M96" s="122" t="n">
@@ -9999,7 +9934,7 @@
       <c r="G104" s="155" t="n"/>
       <c r="H104" s="156">
         <f>H11+H28+H60+H77+H100+H102</f>
-        <v>4173260</v>
+        <v>2886290</v>
       </c>
       <c r="I104" s="157" t="inlineStr">
         <is>
@@ -10017,7 +9952,7 @@
       <c r="O104" s="59" t="n"/>
       <c r="P104" s="159">
         <f>P11+P28+P60+P77+P100</f>
-        <v>3021189</v>
+        <v>2123151</v>
       </c>
       <c r="Q104" s="159">
         <f>Q11+Q28+Q60+Q77+Q100</f>
@@ -10029,11 +9964,11 @@
       </c>
       <c r="S104" s="159">
         <f>H104-P104</f>
-        <v>1152071</v>
+        <v>763139</v>
       </c>
       <c r="T104" s="160">
         <f>IF(H104=0,"",S104/H104)</f>
-        <v>0.2760602023358238</v>
+        <v>0.26440135953074706</v>
       </c>
       <c r="U104" s="59" t="n"/>
       <c r="V104" s="59" t="n"/>
@@ -10500,7 +10435,7 @@
       </c>
       <c r="C17" s="72">
         <f>ROUNDDOWN(C16*'表紙(工事)'!K30/'表紙(工事)'!K28,0)</f>
-        <v>971545</v>
+        <v>1004413</v>
       </c>
       <c r="D17" s="71" t="n"/>
       <c r="E17" s="176" t="inlineStr">
@@ -10561,7 +10496,7 @@
       </c>
       <c r="C22" s="43">
         <f>$C$17</f>
-        <v>971545</v>
+        <v>1004413</v>
       </c>
       <c r="D22" s="38" t="n"/>
       <c r="E22" s="181" t="n">
@@ -10569,7 +10504,7 @@
       </c>
       <c r="F22" s="43">
         <f>ROUNDDOWN(C22*E22,0)</f>
-        <v>47508</v>
+        <v>49115</v>
       </c>
       <c r="G22" s="182" t="inlineStr">
         <is>
@@ -10585,7 +10520,7 @@
       </c>
       <c r="C23" s="43">
         <f>$C$17</f>
-        <v>971545</v>
+        <v>1004413</v>
       </c>
       <c r="D23" s="38" t="n"/>
       <c r="E23" s="181" t="n">
@@ -10593,7 +10528,7 @@
       </c>
       <c r="F23" s="43">
         <f>ROUNDDOWN(C23*E23,0)</f>
-        <v>7869</v>
+        <v>8135</v>
       </c>
       <c r="G23" s="182" t="inlineStr">
         <is>
@@ -10609,7 +10544,7 @@
       </c>
       <c r="C24" s="43">
         <f>$C$17</f>
-        <v>971545</v>
+        <v>1004413</v>
       </c>
       <c r="D24" s="38" t="n"/>
       <c r="E24" s="181" t="n">
@@ -10617,7 +10552,7 @@
       </c>
       <c r="F24" s="43">
         <f>ROUNDDOWN(C24*E24,0)</f>
-        <v>1117</v>
+        <v>1155</v>
       </c>
       <c r="G24" s="182" t="inlineStr">
         <is>
@@ -10633,7 +10568,7 @@
       </c>
       <c r="C25" s="43">
         <f>$C$17</f>
-        <v>971545</v>
+        <v>1004413</v>
       </c>
       <c r="D25" s="38" t="n"/>
       <c r="E25" s="181" t="n">
@@ -10641,7 +10576,7 @@
       </c>
       <c r="F25" s="43">
         <f>ROUNDDOWN(C25*E25,0)</f>
-        <v>88896</v>
+        <v>91903</v>
       </c>
       <c r="G25" s="182" t="inlineStr">
         <is>
@@ -10657,7 +10592,7 @@
       </c>
       <c r="C26" s="43">
         <f>$C$17</f>
-        <v>971545</v>
+        <v>1004413</v>
       </c>
       <c r="D26" s="38" t="n"/>
       <c r="E26" s="181" t="n">
@@ -10665,7 +10600,7 @@
       </c>
       <c r="F26" s="43">
         <f>ROUNDDOWN(C26*E26,0)</f>
-        <v>10201</v>
+        <v>10546</v>
       </c>
       <c r="G26" s="182" t="inlineStr">
         <is>
@@ -10681,7 +10616,7 @@
       </c>
       <c r="C27" s="173">
         <f>$C$17</f>
-        <v>971545</v>
+        <v>1004413</v>
       </c>
       <c r="D27" s="64" t="n"/>
       <c r="E27" s="183" t="n">
@@ -10689,7 +10624,7 @@
       </c>
       <c r="F27" s="173">
         <f>ROUNDDOWN(C27*E27,0)</f>
-        <v>3497</v>
+        <v>3615</v>
       </c>
       <c r="G27" s="184" t="inlineStr">
         <is>
@@ -10711,7 +10646,7 @@
       </c>
       <c r="F28" s="72">
         <f>SUM(F22:F27)</f>
-        <v>159088</v>
+        <v>164469</v>
       </c>
       <c r="G28" s="177" t="n"/>
     </row>
@@ -10851,7 +10786,7 @@
       </c>
       <c r="B8" s="189" t="inlineStr">
         <is>
-          <t>機器の単価は、空調機はVE案の定価、換気機器は三菱電機の価格（税別）に掛率を乗じたものです。機器のメーカー価格改定（三菱電機は2027年1月1日改定予定）が生じた場合は御協議させていただきます。</t>
+          <t>機器の単価は、メーカー定価（空調機はVE案の定価、換気機器は三菱電機の価格〔税別〕）を基準に当社にて算定しています。機器のメーカー価格改定（三菱電機は2027年1月1日改定予定）が生じた場合は御協議させていただきます。</t>
         </is>
       </c>
     </row>
@@ -11508,25 +11443,21 @@
       </c>
       <c r="F4" s="116">
         <f>'内訳書(空調設備工事)'!G7</f>
-        <v>759600</v>
+        <v>316500</v>
       </c>
       <c r="G4" s="201">
         <f>'内訳書(空調設備工事)'!H7</f>
-        <v>1519200</v>
+        <v>633000</v>
       </c>
       <c r="H4" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I4" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I4" s="143" t="n"/>
       <c r="J4" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 1,266,000円 × 提出率 0.60（VE案 8月10日付 定価）</t>
+          <t>原価基準: 定価 1,266,000円（VE案 8月10日付 定価）× 仕入率 0.20（ダイキン業務用（EcoZEAS・FIVESTAR））＝原価 253,200円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -11557,25 +11488,21 @@
       </c>
       <c r="F5" s="116">
         <f>'内訳書(空調設備工事)'!G9</f>
-        <v>228000</v>
+        <v>142500</v>
       </c>
       <c r="G5" s="201">
         <f>'内訳書(空調設備工事)'!H9</f>
-        <v>456000</v>
+        <v>285000</v>
       </c>
       <c r="H5" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I5" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I5" s="143" t="n"/>
       <c r="J5" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 380,000円 × 提出率 0.60（VE案 8月10日付 定価）</t>
+          <t>原価基準: 定価 380,000円（VE案 8月10日付 定価）× 仕入率 0.30（ダイキン家庭用（定価あり））＝原価 114,000円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -11606,25 +11533,21 @@
       </c>
       <c r="F6" s="116">
         <f>'内訳書(空調設備工事)'!G10</f>
-        <v>270000</v>
+        <v>168750</v>
       </c>
       <c r="G6" s="201">
         <f>'内訳書(空調設備工事)'!H10</f>
-        <v>270000</v>
+        <v>168750</v>
       </c>
       <c r="H6" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I6" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I6" s="143" t="n"/>
       <c r="J6" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 450,000円 × 提出率 0.60（VE案 8月10日付 定価）</t>
+          <t>原価基準: 定価 450,000円（VE案 8月10日付 定価）× 仕入率 0.30（ダイキン家庭用（定価あり））＝原価 135,000円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12563,25 +12486,21 @@
       </c>
       <c r="F27" s="116">
         <f>'内訳書(空調設備工事)'!G64</f>
-        <v>7380</v>
+        <v>4920</v>
       </c>
       <c r="G27" s="201">
         <f>'内訳書(空調設備工事)'!H64</f>
-        <v>22140</v>
+        <v>14760</v>
       </c>
       <c r="H27" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I27" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I27" s="143" t="n"/>
       <c r="J27" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 12,300円 × 提出率 0.60（三菱電機 WIN2K 価格（税別））</t>
+          <t>原価基準: 定価 12,300円（三菱電機 WIN2K 価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 3,936円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12612,25 +12531,21 @@
       </c>
       <c r="F28" s="116">
         <f>'内訳書(空調設備工事)'!G66</f>
-        <v>23880</v>
+        <v>15920</v>
       </c>
       <c r="G28" s="201">
         <f>'内訳書(空調設備工事)'!H66</f>
-        <v>119400</v>
+        <v>79600</v>
       </c>
       <c r="H28" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I28" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I28" s="143" t="n"/>
       <c r="J28" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 39,800円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 39,800円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 12,736円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12661,25 +12576,21 @@
       </c>
       <c r="F29" s="116">
         <f>'内訳書(空調設備工事)'!G67</f>
-        <v>15120</v>
+        <v>10080</v>
       </c>
       <c r="G29" s="201">
         <f>'内訳書(空調設備工事)'!H67</f>
-        <v>15120</v>
+        <v>10080</v>
       </c>
       <c r="H29" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I29" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I29" s="143" t="n"/>
       <c r="J29" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 25,200円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 25,200円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 8,064円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12710,25 +12621,21 @@
       </c>
       <c r="F30" s="116">
         <f>'内訳書(空調設備工事)'!G68</f>
-        <v>12420</v>
+        <v>8280</v>
       </c>
       <c r="G30" s="201">
         <f>'内訳書(空調設備工事)'!H68</f>
-        <v>12420</v>
+        <v>8280</v>
       </c>
       <c r="H30" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I30" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I30" s="143" t="n"/>
       <c r="J30" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 20,700円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 20,700円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 6,624円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12759,25 +12666,21 @@
       </c>
       <c r="F31" s="116">
         <f>'内訳書(空調設備工事)'!G70</f>
-        <v>6540</v>
+        <v>4360</v>
       </c>
       <c r="G31" s="201">
         <f>'内訳書(空調設備工事)'!H70</f>
-        <v>26160</v>
+        <v>17440</v>
       </c>
       <c r="H31" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I31" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I31" s="143" t="n"/>
       <c r="J31" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 10,900円 × 提出率 0.60（三菱電機 WIN2K 価格（税別））</t>
+          <t>原価基準: 定価 10,900円（三菱電機 WIN2K 価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 3,488円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12808,25 +12711,21 @@
       </c>
       <c r="F32" s="116">
         <f>'内訳書(空調設備工事)'!G71</f>
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="G32" s="201">
         <f>'内訳書(空調設備工事)'!H71</f>
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="H32" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I32" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I32" s="143" t="n"/>
       <c r="J32" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 6,000円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 6,000円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 1,920円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12857,25 +12756,21 @@
       </c>
       <c r="F33" s="116">
         <f>'内訳書(空調設備工事)'!G72</f>
-        <v>2760</v>
+        <v>1840</v>
       </c>
       <c r="G33" s="201">
         <f>'内訳書(空調設備工事)'!H72</f>
-        <v>8280</v>
+        <v>5520</v>
       </c>
       <c r="H33" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I33" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I33" s="143" t="n"/>
       <c r="J33" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 4,600円 × 提出率 0.60（販売店掲載の参考基準価格（税別）（税込5,060円））</t>
+          <t>原価基準: 定価 4,600円（販売店掲載の参考基準価格（税別）（税込5,060円））× 仕入率 0.32（三菱電機 換気機器）＝原価 1,472円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12906,25 +12801,21 @@
       </c>
       <c r="F34" s="116">
         <f>'内訳書(空調設備工事)'!G74</f>
-        <v>6300</v>
+        <v>4200</v>
       </c>
       <c r="G34" s="201">
         <f>'内訳書(空調設備工事)'!H74</f>
-        <v>50400</v>
+        <v>33600</v>
       </c>
       <c r="H34" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I34" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I34" s="143" t="n"/>
       <c r="J34" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 10,500円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 10,500円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 3,360円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -12955,25 +12846,21 @@
       </c>
       <c r="F35" s="116">
         <f>'内訳書(空調設備工事)'!G75</f>
-        <v>7980</v>
+        <v>5320</v>
       </c>
       <c r="G35" s="201">
         <f>'内訳書(空調設備工事)'!H75</f>
-        <v>47880</v>
+        <v>31920</v>
       </c>
       <c r="H35" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I35" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I35" s="143" t="n"/>
       <c r="J35" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 13,300円 × 提出率 0.60（三菱電機 WIN2K 価格（税別））</t>
+          <t>原価基準: 定価 13,300円（三菱電機 WIN2K 価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 4,256円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -13004,25 +12891,21 @@
       </c>
       <c r="F36" s="116">
         <f>'内訳書(空調設備工事)'!G76</f>
-        <v>20040</v>
+        <v>13360</v>
       </c>
       <c r="G36" s="201">
         <f>'内訳書(空調設備工事)'!H76</f>
-        <v>80160</v>
+        <v>53440</v>
       </c>
       <c r="H36" s="120" t="inlineStr">
         <is>
-          <t>推定（要確認）</t>
-        </is>
-      </c>
-      <c r="I36" s="202" t="inlineStr">
-        <is>
-          <t>単価要確認（推定）</t>
-        </is>
-      </c>
+          <t>原価基準（仕入率）</t>
+        </is>
+      </c>
+      <c r="I36" s="143" t="n"/>
       <c r="J36" s="124" t="inlineStr">
         <is>
-          <t>推定: 定価 33,400円 × 提出率 0.60（販売店掲載の参考基準価格（税別））</t>
+          <t>原価基準: 定価 33,400円（販売店掲載の参考基準価格（税別））× 仕入率 0.32（三菱電機 換気機器）＝原価 10,688円 ÷（1－目標粗利率 0.20）</t>
         </is>
       </c>
     </row>
@@ -13708,7 +13591,7 @@
     <row r="57">
       <c r="A57" s="209" t="inlineStr">
         <is>
-          <t>・機器（１ 空調設備機器・４ 換気設備機器）: 提出単価＝定価×0.60、原価＝定価×0.45（仕入率は想定・要確認）。部門内経費・工事諸経費の対象外</t>
+          <t>・機器（１ 空調設備機器・４ 換気設備機器）: 原価＝定価×仕入率（ダイキン業務用0.20・家庭用0.30・三菱電機換気0.32）、提出単価＝原価÷（1－目標粗利率0.20）を10円未満切上げ。部門内経費・工事諸経費の対象外</t>
         </is>
       </c>
     </row>
@@ -15046,7 +14929,7 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="217" t="inlineStr">
         <is>
-          <t>・機器: 原価＝定価×仕入率0.45（想定）。提出単価＝定価×0.60。内訳書 L 列は「提出単価×材料原価率×0.75」</t>
+          <t>・機器: 原価＝定価×仕入率（ダイキン業務用 EcoZEAS・FIVESTAR 0.20、ダイキン家庭用 0.30、三菱電機 換気機器 0.32）。内訳書 L 列＝原価（定額）、提出単価＝原価÷（1－0.20）の10円未満切上げ</t>
         </is>
       </c>
     </row>

--- a/estimates/安楽寺本堂_空調換気設備工事/御見積書_安楽寺本堂新築工事_空調換気設備工事_20261009.xlsx
+++ b/estimates/安楽寺本堂_空調換気設備工事/御見積書_安楽寺本堂新築工事_空調換気設備工事_20261009.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'内訳書(空調設備工事)'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'内訳書(空調設備工事)'!$A$1:$I$104</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'法定福利費内訳明細書'!$B$1:$G$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'御見積条件'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'御見積条件'!$A$1:$F$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'単価出典(内部)'!$A$1:$J$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'エストマスタ(参考)'!$A$1:$C$17</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'数量拾い根拠(内部)'!$A$1:$F$38</definedName>
@@ -2018,6 +2018,11 @@
           <t>御協議による</t>
         </is>
       </c>
+      <c r="M16" s="28" t="inlineStr">
+        <is>
+          <t>※ 機器（１・４）は原価基準: 原価＝定価×仕入率（ダイキン業務用0.20・家庭用0.30・三菱電機換気0.32）、単価＝原価÷（1－0.20）。小計のうち機器分はエスト定価ベースではない</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
@@ -2028,6 +2033,11 @@
       <c r="D17" s="25" t="inlineStr">
         <is>
           <t>10日</t>
+        </is>
+      </c>
+      <c r="M17" s="28" t="inlineStr">
+        <is>
+          <t>※ 機器の原価は定額（内訳書 L 列）のため材料原価率 N7 の影響を受けない。目標粗利率 N4 を変えた場合は job.py から再生成</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11281,20 +11291,8 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="35.5" customHeight="1">
-      <c r="A39" s="188" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B39" s="189" t="inlineStr">
-        <is>
-          <t>機器の型番・価格（特に空調機のVE案定価、三菱電機機器の価格）は提出前に最新の価格表で確認します。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="30">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
@@ -11302,7 +11300,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="B14:F14"/>
